--- a/data/trans_orig/P16A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45223</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51906</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84507</t>
+          <t>83695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>986500</t>
+          <t>985386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1008746</t>
+          <t>1009247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1270027</t>
+          <t>1269768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1292577</t>
+          <t>1292716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2262328</t>
+          <t>2263140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2294929</t>
+          <t>2294941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43732</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73466</t>
+          <t>74700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1660970</t>
+          <t>1659692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1679119</t>
+          <t>1678600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1538244</t>
+          <t>1539059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1564103</t>
+          <t>1563245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3206601</t>
+          <t>3205367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3236335</t>
+          <t>3235963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539821</t>
+          <t>540804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549894</t>
+          <t>550335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464434</t>
+          <t>464900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>474276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1008574</t>
+          <t>1009246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022815</t>
+          <t>1022814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>155307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3200957</t>
+          <t>3200466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3229743</t>
+          <t>3230214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3285617</t>
+          <t>3285654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3321131</t>
+          <t>3319925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6496235</t>
+          <t>6499415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6542675</t>
+          <t>6542531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46676</t>
+          <t>47366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>48500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52302</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87502</t>
+          <t>85416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>922969</t>
+          <t>922279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>948345</t>
+          <t>947296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1284777</t>
+          <t>1285132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1309143</t>
+          <t>1308789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2215776</t>
+          <t>2217862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2250976</t>
+          <t>2250925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71975</t>
+          <t>72925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74624</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91974</t>
+          <t>93358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136887</t>
+          <t>138249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1887153</t>
+          <t>1886203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1918954</t>
+          <t>1919275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1676227</t>
+          <t>1673879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1708004</t>
+          <t>1706518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3573093</t>
+          <t>3571731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3618006</t>
+          <t>3616622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,47 +3037,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6854</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13996</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6854</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15879</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462452</t>
+          <t>462806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477204</t>
+          <t>477002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,49 +3150,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>450800</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>443658</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>454664</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>450800</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>441775</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>454936</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>835</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>911101</t>
+          <t>910549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>929497</t>
+          <t>929397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77738</t>
+          <t>77113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119220</t>
+          <t>119499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>79906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123886</t>
+          <t>124321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170160</t>
+          <t>170256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229323</t>
+          <t>231256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3289886</t>
+          <t>3289607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331368</t>
+          <t>3331993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3418252</t>
+          <t>3417817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3459732</t>
+          <t>3462232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6721921</t>
+          <t>6719988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6781084</t>
+          <t>6780988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>738376</t>
+          <t>737833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749496</t>
+          <t>749346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>960149</t>
+          <t>959827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>980022</t>
+          <t>980090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1703827</t>
+          <t>1705104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1727999</t>
+          <t>1727176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29614</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53814</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68874</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>108108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2015346</t>
+          <t>2016410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2042917</t>
+          <t>2043782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1934486</t>
+          <t>1932768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1958686</t>
+          <t>1958178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3957721</t>
+          <t>3956577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3995811</t>
+          <t>3994155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>41504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522785</t>
+          <t>522720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539459</t>
+          <t>539198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524372</t>
+          <t>525160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541761</t>
+          <t>541229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054903</t>
+          <t>1054523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077118</t>
+          <t>1077580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53573</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86115</t>
+          <t>86888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61414</t>
+          <t>61160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97199</t>
+          <t>97641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123331</t>
+          <t>123705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175181</t>
+          <t>174955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3291503</t>
+          <t>3290730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3324045</t>
+          <t>3324383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3434901</t>
+          <t>3434459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3470686</t>
+          <t>3470940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6734537</t>
+          <t>6734763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6786387</t>
+          <t>6786013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>58043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>83459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>483705</t>
+          <t>482601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500731</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693898</t>
+          <t>693689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>722656</t>
+          <t>722100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1183911</t>
+          <t>1181724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1218700</t>
+          <t>1218893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66811</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72477</t>
+          <t>70243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79934</t>
+          <t>79237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127016</t>
+          <t>127188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2223516</t>
+          <t>2223678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2259143</t>
+          <t>2260090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2164668</t>
+          <t>2166902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2197002</t>
+          <t>2199331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4400456</t>
+          <t>4400284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4447538</t>
+          <t>4448235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631848</t>
+          <t>631697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642967</t>
+          <t>643061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637302</t>
+          <t>638153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650988</t>
+          <t>651272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274115</t>
+          <t>1272968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291545</t>
+          <t>1291408</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56888</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96559</t>
+          <t>95804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87593</t>
+          <t>90587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>136173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156341</t>
+          <t>152992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220626</t>
+          <t>218504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3353843</t>
+          <t>3354598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3393514</t>
+          <t>3395754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3516177</t>
+          <t>3513166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3561746</t>
+          <t>3558752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6879116</t>
+          <t>6881238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6943401</t>
+          <t>6946750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45345</t>
+          <t>47002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83695</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985386</t>
+          <t>987732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1009247</t>
+          <t>1009355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1269768</t>
+          <t>1268111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1292716</t>
+          <t>1291304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2263140</t>
+          <t>2262367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2294941</t>
+          <t>2295383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44104</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74700</t>
+          <t>74533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1659692</t>
+          <t>1660649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1678600</t>
+          <t>1678420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1539059</t>
+          <t>1539304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1563245</t>
+          <t>1562697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3205367</t>
+          <t>3205534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3235963</t>
+          <t>3236389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540804</t>
+          <t>540295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550335</t>
+          <t>549933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464900</t>
+          <t>464312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474276</t>
+          <t>473754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1009246</t>
+          <t>1009985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022814</t>
+          <t>1022800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93543</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155307</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3200466</t>
+          <t>3198822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3230214</t>
+          <t>3229717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3285654</t>
+          <t>3285484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3319925</t>
+          <t>3321668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6499415</t>
+          <t>6495438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6542531</t>
+          <t>6542014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47366</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>49772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85416</t>
+          <t>87248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>922279</t>
+          <t>923363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>947296</t>
+          <t>947183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1285132</t>
+          <t>1283860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1308789</t>
+          <t>1308585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2217862</t>
+          <t>2216030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2250925</t>
+          <t>2250752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72925</t>
+          <t>74599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,82 +2694,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>59035</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44742</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79002</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>113545</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>92264</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>138025</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>59035</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>44333</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>76972</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>113545</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>93358</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>138249</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1886203</t>
+          <t>1884529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1919275</t>
+          <t>1918326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,82 +2807,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1691816</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1671849</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1706109</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3596435</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3571955</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3617716</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>96,28%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1691816</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1673879</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1706518</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3596435</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3571731</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3616622</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462806</t>
+          <t>460499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477002</t>
+          <t>476359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443658</t>
+          <t>442865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454664</t>
+          <t>454873</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>910549</t>
+          <t>910111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>929397</t>
+          <t>929993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77113</t>
+          <t>77692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119499</t>
+          <t>120791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79906</t>
+          <t>82634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124321</t>
+          <t>125505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170256</t>
+          <t>172046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231256</t>
+          <t>229515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3289607</t>
+          <t>3288315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331993</t>
+          <t>3331414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3417817</t>
+          <t>3416633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3462232</t>
+          <t>3459504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6719988</t>
+          <t>6721729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6780988</t>
+          <t>6779198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>45194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>737833</t>
+          <t>737853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749346</t>
+          <t>749724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>959827</t>
+          <t>960347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>980090</t>
+          <t>980330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1705104</t>
+          <t>1703813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1727176</t>
+          <t>1727190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59975</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55532</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70530</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108108</t>
+          <t>107598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2016410</t>
+          <t>2015206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2043782</t>
+          <t>2043993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1932768</t>
+          <t>1932484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1958178</t>
+          <t>1958500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3956577</t>
+          <t>3957087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3994155</t>
+          <t>3995760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41504</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522720</t>
+          <t>522446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539198</t>
+          <t>538960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525160</t>
+          <t>523890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541229</t>
+          <t>541013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054523</t>
+          <t>1054907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077580</t>
+          <t>1077071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>53475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86888</t>
+          <t>88669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61160</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97641</t>
+          <t>99772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123705</t>
+          <t>125116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174955</t>
+          <t>172196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3290730</t>
+          <t>3288949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3324383</t>
+          <t>3324143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3434459</t>
+          <t>3432328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3470940</t>
+          <t>3469869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6734763</t>
+          <t>6737522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6786013</t>
+          <t>6784602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>31414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>50682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46290</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83459</t>
+          <t>77108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>493311</t>
+          <t>555205</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482601</t>
+          <t>545633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>500543</t>
+          <t>562928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>712018</t>
+          <t>780009</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693689</t>
+          <t>769103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>722100</t>
+          <t>789554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1205328</t>
+          <t>1335215</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181724</t>
+          <t>1319724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1218893</t>
+          <t>1347345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751732</t>
+          <t>819785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265183</t>
+          <t>1396832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66649</t>
+          <t>72230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>102964</t>
+          <t>115571</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79237</t>
+          <t>96060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127188</t>
+          <t>137194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2243007</t>
+          <t>2177945</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2223678</t>
+          <t>2158336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2260090</t>
+          <t>2191037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2181501</t>
+          <t>2107757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2166902</t>
+          <t>2093514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2199331</t>
+          <t>2120679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4424508</t>
+          <t>4285703</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4400284</t>
+          <t>4264080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4448235</t>
+          <t>4305214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>638889</t>
+          <t>703902</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631697</t>
+          <t>697549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643061</t>
+          <t>707860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>645257</t>
+          <t>714668</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638153</t>
+          <t>703831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651272</t>
+          <t>721786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1284146</t>
+          <t>1418570</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272968</t>
+          <t>1406680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291408</t>
+          <t>1426618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>64166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95804</t>
+          <t>103773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>110564</t>
+          <t>122935</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90587</t>
+          <t>104303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136173</t>
+          <t>143613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>205082</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152992</t>
+          <t>180038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218504</t>
+          <t>235642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3375208</t>
+          <t>3437052</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3354598</t>
+          <t>3415427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3395754</t>
+          <t>3455034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3538775</t>
+          <t>3602434</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3513166</t>
+          <t>3581756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3558752</t>
+          <t>3621066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6913983</t>
+          <t>7039488</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6881238</t>
+          <t>7008928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6946750</t>
+          <t>7064532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649339</t>
+          <t>3725369</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099742</t>
+          <t>7244570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
